--- a/Dataset/IT/xlsx/ITAMed_2017.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2017.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Oncologia</t>
+          <t>Ginecologia e Ostetricia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Chirurgia Generale</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Oncologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Pneumologia e Chirurgia Toracica; Oncologia</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Pneumologia e Chirurgia Toracica; Oncologia</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Farmacologia e Tossicologia</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Oncologia</t>
+          <t>Oncologia; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Pediatria; Chirurgia Generale</t>
+          <t>Pediatria; Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Igiene, Epidemiologia e Statistica; Medicina del Lavoro</t>
+          <t>Malattie Infettive; Igiene, Epidemiologia e Statistica</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Cardiologia e Cardiochirurgia</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Gastroenterologia</t>
+          <t>Gastroenterologia; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Endocrinologia; Farmacologia e Tossicologia</t>
+          <t>Medicina Interna</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Endocrinologia; Nefrologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Anestesia e Rianimazione</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Oncologia; Gastroenterologia</t>
+          <t>Gastroenterologia; Oncologia</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Oncologia; Farmacologia e Tossicologia</t>
+          <t>Oncologia</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Oncologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Oncologia; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Endocrinologia; Pediatria</t>
+          <t>Pediatria; Endocrinologia</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Endocrinologia; Pediatria</t>
+          <t>Pediatria</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Pediatria; Urologia</t>
+          <t>Pediatria; Nefrologia</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Pediatria; Urologia</t>
+          <t>Pediatria; Malattie Infettive</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Psichiatria; Farmacologia e Tossicologia</t>
+          <t>Psichiatria</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Urologia; Diagnostica per Immagini e Medicina Nucleare</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Urologia; Farmacologia e Tossicologia</t>
+          <t>Urologia</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_2017.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2017.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Immagine</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/IT/xlsx/ITAMed_2017.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2017.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" bestFit="1" customWidth="1" min="13" max="13"/>
@@ -477,15 +477,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Tipo Domanda</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Immagine</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Categoria Immagine</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Percorso Immagine</t>
         </is>
@@ -548,6 +553,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -606,6 +616,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -664,6 +679,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -719,7 +739,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -777,7 +802,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -840,10 +870,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>images/2017/ssm201711.png</t>
         </is>
@@ -908,10 +943,15 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>images/2017/ssm201712.png</t>
         </is>
@@ -974,6 +1014,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1032,6 +1077,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1090,6 +1140,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1148,6 +1203,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1206,6 +1266,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1264,6 +1329,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1322,6 +1392,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1380,6 +1455,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1438,6 +1518,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1496,6 +1581,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1554,6 +1644,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1612,6 +1707,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1670,6 +1770,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1728,6 +1833,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1786,6 +1896,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1844,6 +1959,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1902,6 +2022,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1960,6 +2085,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2018,6 +2148,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2076,6 +2211,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2134,6 +2274,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2192,6 +2337,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2250,6 +2400,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2310,10 +2465,15 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>images/2017/ssm201760.png</t>
         </is>
@@ -2378,10 +2538,15 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>images/2017/ssm201761.png</t>
         </is>
@@ -2444,6 +2609,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2502,6 +2672,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2560,6 +2735,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2618,6 +2798,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2676,6 +2861,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2734,6 +2924,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2792,6 +2987,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2850,6 +3050,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2908,6 +3113,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2966,6 +3176,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3024,6 +3239,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3079,7 +3299,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3140,6 +3365,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3198,6 +3428,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3256,6 +3491,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3314,6 +3554,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3372,6 +3617,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3430,6 +3680,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3488,6 +3743,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3546,6 +3806,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3606,10 +3871,15 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>Clinical study table</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>images/2017/ssm2017106.png</t>
         </is>
@@ -3674,10 +3944,15 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
           <t>Clinical study table</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>images/2017/ssm2017107.png</t>
         </is>
@@ -3740,6 +4015,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3798,6 +4078,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3856,6 +4141,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3914,6 +4204,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3972,6 +4267,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4030,6 +4330,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4088,6 +4393,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4146,6 +4456,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4206,10 +4521,15 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>images/2017/ssm2017126.png</t>
         </is>
@@ -4274,10 +4594,15 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>images/2017/ssm2017127.png</t>
         </is>
@@ -4342,10 +4667,15 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
           <t>ECG tracing</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>images/2017/ssm2017128.png</t>
         </is>
@@ -4408,6 +4738,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4466,6 +4801,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4524,6 +4864,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4582,6 +4927,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4640,6 +4990,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4698,6 +5053,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4756,6 +5116,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4814,6 +5179,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4872,6 +5242,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4930,6 +5305,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4988,6 +5368,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5046,6 +5431,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5104,6 +5494,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5162,6 +5557,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5220,6 +5620,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5278,6 +5683,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5336,6 +5746,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5394,6 +5809,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5452,6 +5872,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5510,6 +5935,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5568,6 +5998,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5626,6 +6061,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5684,6 +6124,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5742,6 +6187,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5800,6 +6250,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5858,6 +6313,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5916,6 +6376,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5974,6 +6439,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6032,6 +6502,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6092,10 +6567,15 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>images/2017/ssm2017189.png</t>
         </is>
@@ -6158,6 +6638,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6216,6 +6701,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6274,6 +6764,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6332,6 +6827,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6390,6 +6890,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6448,6 +6953,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6506,6 +7016,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6564,6 +7079,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6622,6 +7142,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6680,6 +7205,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6738,6 +7268,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6796,6 +7331,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6854,6 +7394,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6912,6 +7457,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6970,6 +7520,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7030,10 +7585,15 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
           <t>Upper limb X-ray</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr">
+      <c r="O112" t="inlineStr">
         <is>
           <t>images/2017/ssm2017217.png</t>
         </is>
@@ -7096,6 +7656,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7154,6 +7719,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7212,6 +7782,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7270,6 +7845,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7328,6 +7908,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7386,6 +7971,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7444,6 +8034,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7502,6 +8097,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7560,6 +8160,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7618,6 +8223,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7676,6 +8286,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7734,6 +8349,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7792,6 +8412,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7850,6 +8475,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7908,6 +8538,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7966,6 +8601,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -8024,6 +8664,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8082,6 +8727,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8142,10 +8792,15 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
           <t>Spine MRI</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr">
+      <c r="O131" t="inlineStr">
         <is>
           <t>images/2017/ssm2017256.png</t>
         </is>
@@ -8210,10 +8865,15 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
           <t>Spine MRI</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr">
+      <c r="O132" t="inlineStr">
         <is>
           <t>images/2017/ssm2017257.png</t>
         </is>
@@ -8276,6 +8936,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8334,6 +8999,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8392,6 +9062,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8450,6 +9125,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8510,10 +9190,15 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
           <t>Endoscopic image</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr">
+      <c r="O137" t="inlineStr">
         <is>
           <t>images/2017/ssm2017271.png</t>
         </is>
@@ -8576,6 +9261,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8634,6 +9324,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8692,6 +9387,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8748,6 +9448,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>case-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
